--- a/Luban/Data/#combatnum.xlsx
+++ b/Luban/Data/#combatnum.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,25 +444,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>hitscan_radius</t>
+          <t>base_damage</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>hitscan_height</t>
+          <t>damage_spread</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>base_damage</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>damage_spread</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>entity_hp</t>
         </is>
@@ -496,25 +486,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -548,25 +528,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>[射击] 命中圆柱半径 m</t>
+          <t>[伤害] 命中基础值</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[射击] 命中圆柱高度 m</t>
+          <t>[伤害] ± 浮动幅度（0=无浮动）</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>[伤害] 命中基础值</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>[伤害] ± 浮动幅度（0=无浮动）</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
         <is>
           <t>[出生] 实体初始 HP</t>
         </is>
@@ -586,18 +556,12 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
         <v>100</v>
       </c>
     </row>
